--- a/AAII_Financials/Quarterly/IFNNY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IFNNY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="92">
   <si>
     <t>IFNNY</t>
   </si>
@@ -656,13 +656,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -689,133 +689,148 @@
     <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -849,86 +864,98 @@
       <c r="M8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R8" s="3">
         <v>4376100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>4477300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>3936700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>3578300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>3427500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>3259900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>2879900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>2756200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>2685700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>2584400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>2371600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>2242400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>2236800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>2525900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>2370400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>2332800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>2330300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>2421400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>2131200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AK8" s="3">
         <v>2060000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AL8" s="3">
         <v>1991500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AM8" s="3">
         <v>6136200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AN8" s="3">
         <v>2054400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AO8" s="3">
         <v>4006200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AP8" s="3">
         <v>1932100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AQ8" s="3">
         <v>1966100</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,86 +989,98 @@
       <c r="M9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R9" s="3">
         <v>2309300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>2488900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>2235000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>2042000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>2004000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>1917800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>1753100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>1763900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>1680200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>1761300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>1731300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>1467800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>1409100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AE9" s="3">
         <v>1630500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>1505800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>1451700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>1408800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>1458500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>1316500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AK9" s="3">
         <v>1294800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AL9" s="3">
         <v>1266700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AM9" s="3">
         <v>3817000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AN9" s="3">
         <v>1269000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AO9" s="3">
         <v>2554200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AP9" s="3">
         <v>1237200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AQ9" s="3">
         <v>1252500</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1075,86 +1114,98 @@
       <c r="M10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R10" s="3">
         <v>2066800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>1988500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>1701800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>1536400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>1423500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>1342100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>1126800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>992200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>1005500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>823100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>640400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>774600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>827700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>895500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>864700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>881100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>921500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>962900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>814700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AK10" s="3">
         <v>765200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AL10" s="3">
         <v>724800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AM10" s="3">
         <v>2319200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AN10" s="3">
         <v>785400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AO10" s="3">
         <v>1452000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AP10" s="3">
         <v>694900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AQ10" s="3">
         <v>713700</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1194,8 +1245,12 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1229,86 +1284,98 @@
       <c r="M12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="3">
         <v>536100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
         <v>525200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="T12" s="3">
         <v>507100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <v>480700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="V12" s="3">
         <v>429700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="W12" s="3">
         <v>431500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
         <v>397800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="Y12" s="3">
         <v>345000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="Z12" s="3">
         <v>333800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="AA12" s="3">
         <v>318600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="AB12" s="3">
         <v>350200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AC12" s="3">
         <v>272100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AD12" s="3">
         <v>283700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AE12" s="3">
         <v>281700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AF12" s="3">
         <v>285900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AG12" s="3">
         <v>277600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AH12" s="3">
         <v>279200</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AI12" s="3">
         <v>263800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AJ12" s="3">
         <v>239400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AK12" s="3">
         <v>223300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AL12" s="3">
         <v>218800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AM12" s="3">
         <v>642900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AN12" s="3">
         <v>218800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AO12" s="3">
         <v>460100</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AP12" s="3">
         <v>234800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AQ12" s="3">
         <v>211300</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1420,8 +1487,20 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1458,83 +1537,95 @@
       <c r="N14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>3300</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>3100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>22800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <v>18500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>11300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>10</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM14" s="3" t="s">
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1577,77 +1668,89 @@
       <c r="P15" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="U15" s="3">
         <v>49900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <v>49900</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y15" s="3">
         <v>65300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>70400</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="3">
         <v>20300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AD15" s="3">
         <v>22200</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG15" s="3">
         <v>11800</v>
       </c>
-      <c r="AD15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK15" s="3">
         <v>14600</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ15" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AL15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1684,8 +1787,12 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1719,86 +1826,98 @@
       <c r="M17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R17" s="3">
         <v>3306200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>3482000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>3186000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>2911100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>2758100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>2743900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>2513800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>2438700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>2348900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>2418300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>2491600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>1998500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>1926200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>2224600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>2037500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>1974000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>1943500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>1983700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>1781000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AK17" s="3">
         <v>1463100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AL17" s="3">
         <v>1713300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AM17" s="3">
         <v>5191400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AN17" s="3">
         <v>1720000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AO17" s="3">
         <v>3521400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AP17" s="3">
         <v>1716100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AQ17" s="3">
         <v>1696200</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1832,86 +1951,98 @@
       <c r="M18" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R18" s="3">
         <v>1069900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>995300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>750800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>667300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>669400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>516000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>366100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>317500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>336900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>166100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>-120000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>243900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <v>310500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <v>301300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>332900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>358800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>386800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>437700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>350300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AK18" s="3">
         <v>596900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AL18" s="3">
         <v>278300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AM18" s="3">
         <v>944700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AN18" s="3">
         <v>334400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AO18" s="3">
         <v>484800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AP18" s="3">
         <v>216000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AQ18" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1951,8 +2082,12 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1986,86 +2121,98 @@
       <c r="M20" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="3">
         <v>-23300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="S20" s="3">
         <v>-27000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="T20" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>-27100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="V20" s="3">
         <v>-42300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="W20" s="3">
         <v>-29300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="X20" s="3">
         <v>-55000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="Y20" s="3">
         <v>-40800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="Z20" s="3">
         <v>-25500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="AA20" s="3">
         <v>-15600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="AB20" s="3">
         <v>-67600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AC20" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AD20" s="3">
         <v>-15200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AE20" s="3">
         <v>-24500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AF20" s="3">
         <v>-36500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AG20" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AH20" s="3">
         <v>-20100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AI20" s="3">
         <v>-17700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AJ20" s="3">
         <v>-17600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AK20" s="3">
         <v>-14600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AL20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AM20" s="3">
         <v>-37000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AN20" s="3">
         <v>-12300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AO20" s="3">
         <v>-32900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AP20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AQ20" s="3">
         <v>-18800</v>
       </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2099,86 +2246,98 @@
       <c r="M21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R21" s="3">
         <v>1521800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>1448100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>1176200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>1079600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>1053500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>917100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>713100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>652300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>687000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>543900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AB21" s="3">
         <v>229100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AC21" s="3">
         <v>505800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AD21" s="3">
         <v>587200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AE21" s="3">
         <v>575700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AF21" s="3">
         <v>576400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AG21" s="3">
         <v>621100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>638800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AI21" s="3">
         <v>687300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AJ21" s="3">
         <v>573200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AK21" s="3">
         <v>820200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AL21" s="3">
         <v>491400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AM21" s="3">
         <v>2048800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AN21" s="3">
         <v>94200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AO21" s="3">
         <v>927300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AP21" s="3">
         <v>430800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AQ21" s="3">
         <v>489500</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2212,17 +2371,17 @@
       <c r="M22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2260,11 +2419,11 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE22" s="3" t="s">
-        <v>10</v>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2272,26 +2431,38 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>0</v>
+      <c r="AH22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM22" s="3" t="s">
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ22" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2325,86 +2496,98 @@
       <c r="M23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R23" s="3">
         <v>1046700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>968300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>717100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>640200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>627100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>486800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>311100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>276600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>311300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>150500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>-187600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>224700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AD23" s="3">
         <v>295400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AE23" s="3">
         <v>276800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <v>296500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <v>347000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <v>366700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AI23" s="3">
         <v>419900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AJ23" s="3">
         <v>332700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AK23" s="3">
         <v>582300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AL23" s="3">
         <v>262500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AM23" s="3">
         <v>907700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AN23" s="3">
         <v>322000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AO23" s="3">
         <v>451900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AP23" s="3">
         <v>196000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AQ23" s="3">
         <v>251200</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2438,86 +2621,98 @@
       <c r="M24" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R24" s="3">
         <v>239200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="S24" s="3">
         <v>178300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="T24" s="3">
         <v>145800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="U24" s="3">
         <v>131300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>126900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="W24" s="3">
         <v>-17300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>51800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>63300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>50000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>34300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="AB24" s="3">
         <v>-48000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AC24" s="3">
         <v>23700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AD24" s="3">
         <v>50200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AE24" s="3">
         <v>77200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AF24" s="3">
         <v>32900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AG24" s="3">
         <v>54100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AH24" s="3">
         <v>66200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AI24" s="3">
         <v>63900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AJ24" s="3">
         <v>53800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AK24" s="3">
         <v>69600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AL24" s="3">
         <v>31400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AM24" s="3">
         <v>228900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AN24" s="3">
         <v>41500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AO24" s="3">
         <v>24700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AP24" s="3">
         <v>1200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AQ24" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2629,8 +2824,20 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2664,86 +2871,98 @@
       <c r="M26" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R26" s="3">
         <v>807400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>790000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>571300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>508900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>500200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>504100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>259200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>213300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>261300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>116200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>-139600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>201000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>245200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>199700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AF26" s="3">
         <v>263500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <v>292900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>300500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <v>356100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AJ26" s="3">
         <v>278900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AK26" s="3">
         <v>512700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AL26" s="3">
         <v>231100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AM26" s="3">
         <v>678800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AN26" s="3">
         <v>280500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AO26" s="3">
         <v>427300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AP26" s="3">
         <v>194900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AQ26" s="3">
         <v>267600</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2777,86 +2996,98 @@
       <c r="M27" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R27" s="3">
         <v>799700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>782400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>563600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>501300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>492600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>500900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>250700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>205200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>253200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>109000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>-150500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>189700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>235800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>199700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>263500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>292900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>300500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>356100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AJ27" s="3">
         <v>278900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AK27" s="3">
         <v>512700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AL27" s="3">
         <v>231100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AM27" s="3">
         <v>678800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AN27" s="3">
         <v>280500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AO27" s="3">
         <v>427300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AP27" s="3">
         <v>194900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AQ27" s="3">
         <v>267600</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2968,8 +3199,20 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3003,86 +3246,98 @@
       <c r="M29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R29" s="3">
         <v>-1100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="S29" s="3">
         <v>4300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="T29" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>-4300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="W29" s="3">
         <v>-1100</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-6100</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-3100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-21200</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-188100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AJ29" s="3">
         <v>18700</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3">
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AM29" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AN29" s="3">
         <v>3400</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AO29" s="3">
         <v>-3500</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AP29" s="3">
         <v>-4700</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AQ29" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3194,8 +3449,20 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3307,8 +3574,20 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3342,86 +3621,98 @@
       <c r="M32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R32" s="3">
         <v>23300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="S32" s="3">
         <v>27000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="T32" s="3">
         <v>33700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="U32" s="3">
         <v>27100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="V32" s="3">
         <v>42300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="W32" s="3">
         <v>29300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="X32" s="3">
         <v>55000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="Y32" s="3">
         <v>40800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="Z32" s="3">
         <v>25500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="AA32" s="3">
         <v>15600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="AB32" s="3">
         <v>67600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AC32" s="3">
         <v>19200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AD32" s="3">
         <v>15200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AE32" s="3">
         <v>24500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AF32" s="3">
         <v>36500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AG32" s="3">
         <v>11800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AH32" s="3">
         <v>20100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AI32" s="3">
         <v>17700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AJ32" s="3">
         <v>17600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AK32" s="3">
         <v>14600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AL32" s="3">
         <v>15700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AM32" s="3">
         <v>37000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AN32" s="3">
         <v>12300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AO32" s="3">
         <v>32900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AP32" s="3">
         <v>20000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AQ32" s="3">
         <v>18800</v>
       </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3455,86 +3746,98 @@
       <c r="M33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R33" s="3">
         <v>798600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>786700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>554900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>501300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>488300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>499800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>250700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>199100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>253200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>105900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>-150500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>189700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>235800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>197200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>263500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>271700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>300500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>168000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AJ33" s="3">
         <v>297600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AK33" s="3">
         <v>512700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AL33" s="3">
         <v>230000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AM33" s="3">
         <v>679900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AN33" s="3">
         <v>283900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AO33" s="3">
         <v>423700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AP33" s="3">
         <v>190200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AQ33" s="3">
         <v>264100</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3646,8 +3949,20 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3681,204 +3996,228 @@
       <c r="M35" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R35" s="3">
         <v>798600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>786700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>554900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>501300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>488300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>499800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>250700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>199100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>253200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>105900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>-150500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>189700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>235800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>197200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>263500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>271700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>300500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>168000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AJ35" s="3">
         <v>297600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AK35" s="3">
         <v>512700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AL35" s="3">
         <v>230000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AM35" s="3">
         <v>679900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AN35" s="3">
         <v>283900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AO35" s="3">
         <v>423700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AP35" s="3">
         <v>190200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AQ35" s="3">
         <v>264100</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3918,8 +4257,12 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3959,1025 +4302,1137 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>10</v>
+      <c r="D41" s="3">
+        <v>1220200</v>
       </c>
       <c r="E41" s="3">
+        <v>1498900</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1451200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1591000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1502100</v>
+      </c>
+      <c r="I41" s="3">
         <v>1313200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>1298300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>2014300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>1868600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>1926900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>1776300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1926300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>1660500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>1546100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>1573900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>1554000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>1734400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>1393100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>2165700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>1896100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>2031400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>1912000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>1933400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>1921200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>2671600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>1274800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>1567800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>1250700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>849400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AG41" s="3">
         <v>951700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AH41" s="3">
         <v>978300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AI41" s="3">
         <v>865900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AJ41" s="3">
         <v>846600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AK41" s="3">
         <v>814600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AL41" s="3">
         <v>835900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AM41" s="3">
         <v>964900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AN41" s="3">
         <v>814600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AO41" s="3">
         <v>846300</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM41" s="3">
+      <c r="AP41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ41" s="3">
         <v>733600</v>
       </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>671800</v>
       </c>
       <c r="E42" s="3">
+        <v>983500</v>
+      </c>
+      <c r="F42" s="3">
+        <v>719700</v>
+      </c>
+      <c r="G42" s="3">
+        <v>875300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>305300</v>
+      </c>
+      <c r="I42" s="3">
         <v>510200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>727800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>440600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>644000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>859900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>1221400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>1873400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>1599300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>2198000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="R42" s="3">
         <v>2533100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="S42" s="3">
         <v>2462900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="T42" s="3">
         <v>2149000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="U42" s="3">
         <v>2084300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="V42" s="3">
         <v>2482500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="W42" s="3">
         <v>2355700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="X42" s="3">
         <v>2055700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="Y42" s="3">
         <v>1603700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="Z42" s="3">
         <v>1470000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="AA42" s="3">
         <v>1428200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="AB42" s="3">
         <v>1092000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AC42" s="3">
         <v>3905600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AD42" s="3">
         <v>4104600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AE42" s="3">
         <v>3378500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AF42" s="3">
         <v>3191600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AG42" s="3">
         <v>1262300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AH42" s="3">
         <v>1749500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AI42" s="3">
         <v>2142200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AJ42" s="3">
         <v>2031300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AK42" s="3">
         <v>1920800</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AL42" s="3">
         <v>1758200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AM42" s="3">
         <v>1786200</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AN42" s="3">
         <v>1672900</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AO42" s="3">
         <v>1558800</v>
       </c>
-      <c r="AL42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM42" s="3">
+      <c r="AP42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ42" s="3">
         <v>1895700</v>
       </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>10</v>
+      <c r="D43" s="3">
+        <v>3141800</v>
       </c>
       <c r="E43" s="3">
+        <v>2865200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2543100</v>
+      </c>
+      <c r="G43" s="3">
+        <v>3254700</v>
+      </c>
+      <c r="H43" s="3">
+        <v>2695200</v>
+      </c>
+      <c r="I43" s="3">
         <v>2433000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>2364600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>3089400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>2509400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>2328200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>2125600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>2492600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>2363500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>2295700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>2118800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>2193800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>2108700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>1936700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>1723000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>1758400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>1437800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>1503600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>1323000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>1421900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>1394200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>1402300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>1152200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>1508000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>1248200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AG43" s="3">
         <v>1247000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AH43" s="3">
         <v>1220800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AI43" s="3">
         <v>1210100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AJ43" s="3">
         <v>1046400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AK43" s="3">
         <v>970500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AL43" s="3">
         <v>902100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AM43" s="3">
         <v>3306500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AN43" s="3">
         <v>958200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AO43" s="3">
         <v>970700</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM43" s="3">
+      <c r="AP43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ43" s="3">
         <v>915600</v>
       </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>10</v>
+      <c r="D44" s="3">
+        <v>5176500</v>
       </c>
       <c r="E44" s="3">
+        <v>5234600</v>
+      </c>
+      <c r="F44" s="3">
+        <v>5265900</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4858600</v>
+      </c>
+      <c r="H44" s="3">
+        <v>5026400</v>
+      </c>
+      <c r="I44" s="3">
         <v>4683300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>4539800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>4450100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>4745500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>4751300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>4786100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>4206200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>4098300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>3801600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>3587500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>3329600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>3083700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>2755900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>2516100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>2364400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>2172100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>1977300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>1995700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="AA44" s="3">
         <v>2129800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AB44" s="3">
         <v>2416400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AC44" s="3">
         <v>1960100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AD44" s="3">
         <v>2062800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AE44" s="3">
         <v>2083700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AF44" s="3">
         <v>2068100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AG44" s="3">
         <v>2006900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AH44" s="3">
         <v>1882000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AI44" s="3">
         <v>1750700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AJ44" s="3">
         <v>1524000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AK44" s="3">
         <v>1464200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AL44" s="3">
         <v>1438400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AM44" s="3">
         <v>1391300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AN44" s="3">
         <v>1396900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AO44" s="3">
         <v>1441400</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM44" s="3">
+      <c r="AP44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ44" s="3">
         <v>1398000</v>
       </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>10</v>
+      <c r="D45" s="3">
+        <v>1544600</v>
       </c>
       <c r="E45" s="3">
+        <v>1550800</v>
+      </c>
+      <c r="F45" s="3">
+        <v>1561600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>333200</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1786300</v>
+      </c>
+      <c r="I45" s="3">
         <v>1439700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>1357300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>265400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>1269700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>1190000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>1081000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>292100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>1007600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>838800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>767600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>675400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="T45" s="3">
         <v>706200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>580500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>500200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>571300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>630600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>556300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>538000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <v>550100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AB45" s="3">
         <v>692700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AC45" s="3">
         <v>931500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AD45" s="3">
         <v>735500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AE45" s="3">
         <v>957900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AF45" s="3">
         <v>868200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AG45" s="3">
         <v>641100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AH45" s="3">
         <v>533500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AI45" s="3">
         <v>446000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AJ45" s="3">
         <v>435900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AK45" s="3">
         <v>409500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AL45" s="3">
         <v>410600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AM45" s="3">
         <v>6195600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AN45" s="3">
         <v>356800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AO45" s="3">
         <v>336900</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM45" s="3">
+      <c r="AP45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ45" s="3">
         <v>329800</v>
       </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>10</v>
+      <c r="D46" s="3">
+        <v>11754800</v>
       </c>
       <c r="E46" s="3">
+        <v>12133100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11541600</v>
+      </c>
+      <c r="G46" s="3">
+        <v>11525300</v>
+      </c>
+      <c r="H46" s="3">
+        <v>11315300</v>
+      </c>
+      <c r="I46" s="3">
         <v>10379400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>10287800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>10922400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>11037200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>11056200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>10990400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>11316700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>10729300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>10680100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>10580900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>10215900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>9782000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>8750500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>9387400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>8946000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>8327500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>7552900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>7259900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>7451100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AB46" s="3">
         <v>8266900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AC46" s="3">
         <v>9474300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AD46" s="3">
         <v>9623000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AE46" s="3">
         <v>9178900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AF46" s="3">
         <v>8225400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AG46" s="3">
         <v>6109000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AH46" s="3">
         <v>6364000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AI46" s="3">
         <v>6414900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AJ46" s="3">
         <v>5884200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AK46" s="3">
         <v>5579700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AL46" s="3">
         <v>5345200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AM46" s="3">
         <v>8448600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AN46" s="3">
         <v>5199300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AO46" s="3">
         <v>5154200</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AP46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ46" s="3">
         <v>5272800</v>
       </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>10</v>
+      <c r="D47" s="3">
+        <v>123400</v>
       </c>
       <c r="E47" s="3">
+        <v>128000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>124500</v>
+      </c>
+      <c r="G47" s="3">
+        <v>503300</v>
+      </c>
+      <c r="H47" s="3">
+        <v>115100</v>
+      </c>
+      <c r="I47" s="3">
         <v>109200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>128400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>393700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>127500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>125100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>128200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>340800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>116800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>106500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>109700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>110200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="T47" s="3">
         <v>111000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="U47" s="3">
         <v>99800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="V47" s="3">
         <v>83500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="W47" s="3">
         <v>78100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="X47" s="3">
         <v>66700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="Y47" s="3">
         <v>80600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="Z47" s="3">
         <v>81700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="AA47" s="3">
         <v>91300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="AB47" s="3">
         <v>118900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AC47" s="3">
         <v>82400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AD47" s="3">
         <v>85200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AE47" s="3">
         <v>35500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AF47" s="3">
         <v>43500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AG47" s="3">
         <v>43500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AH47" s="3">
         <v>39000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AI47" s="3">
         <v>43800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AJ47" s="3">
         <v>43900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AK47" s="3">
         <v>42600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AL47" s="3">
         <v>31400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AM47" s="3">
         <v>11876300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AN47" s="3">
         <v>38100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AO47" s="3">
         <v>42300</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AP47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ47" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>10</v>
+      <c r="D48" s="3">
+        <v>10299300</v>
       </c>
       <c r="E48" s="3">
+        <v>10259400</v>
+      </c>
+      <c r="F48" s="3">
+        <v>10291200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>7619400</v>
+      </c>
+      <c r="H48" s="3">
+        <v>9787400</v>
+      </c>
+      <c r="I48" s="3">
         <v>9275800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>8996800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>7222800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>8753900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>8556500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>8512200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>5950500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>7360300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>6900300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>6799600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>6430200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>5873600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>5566100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>5343600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>5180900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>4707000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>4553800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>4469100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>4562600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AB48" s="3">
         <v>4741100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AC48" s="3">
         <v>4239800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AD48" s="3">
         <v>4402300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AE48" s="3">
         <v>4299700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AF48" s="3">
         <v>3993900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AG48" s="3">
         <v>3886800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AH48" s="3">
         <v>3777000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AI48" s="3">
         <v>3593700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AJ48" s="3">
         <v>3132600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AK48" s="3">
         <v>3128100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AL48" s="3">
         <v>3085500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AM48" s="3">
         <v>2983400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AN48" s="3">
         <v>2851000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AO48" s="3">
         <v>2974400</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AP48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ48" s="3">
         <v>2487300</v>
       </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>10</v>
+      <c r="D49" s="3">
+        <v>12884700</v>
       </c>
       <c r="E49" s="3">
+        <v>12954000</v>
+      </c>
+      <c r="F49" s="3">
+        <v>13012800</v>
+      </c>
+      <c r="G49" s="3">
+        <v>11622700</v>
+      </c>
+      <c r="H49" s="3">
+        <v>10649400</v>
+      </c>
+      <c r="I49" s="3">
         <v>10553400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>10541500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>9471300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>10768200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>10823200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>10959400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>9025200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>10233600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>10222700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>10687200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>11418700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="T49" s="3">
         <v>10934300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="U49" s="3">
         <v>10325900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="V49" s="3">
         <v>10232600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="W49" s="3">
         <v>10094100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="X49" s="3">
         <v>9704000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="Y49" s="3">
         <v>9553700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Z49" s="3">
         <v>9230100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AA49" s="3">
         <v>9878700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="AB49" s="3">
         <v>10905800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AC49" s="3">
         <v>4073800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AD49" s="3">
         <v>2085000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AE49" s="3">
         <v>4422200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AF49" s="3">
         <v>2057500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AG49" s="3">
         <v>2068100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AH49" s="3">
         <v>2053500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AI49" s="3">
         <v>1887900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AJ49" s="3">
         <v>1733700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AK49" s="3">
         <v>1705400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AL49" s="3">
         <v>1755900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AM49" s="3">
         <v>1810900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AN49" s="3">
         <v>1819900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AO49" s="3">
         <v>1989600</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AP49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ49" s="3">
         <v>1943800</v>
       </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5089,8 +5544,20 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5202,121 +5669,145 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>10</v>
+      <c r="D52" s="3">
+        <v>799700</v>
       </c>
       <c r="E52" s="3">
+        <v>799000</v>
+      </c>
+      <c r="F52" s="3">
+        <v>820700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2758400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>721100</v>
+      </c>
+      <c r="I52" s="3">
         <v>666900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>547700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>2382300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>511100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>535100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>483000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>2128500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>425800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>375900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>945900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>908900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>953200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>946100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>990600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>997400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="X52" s="3">
         <v>837900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Y52" s="3">
         <v>838100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Z52" s="3">
         <v>834000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AA52" s="3">
         <v>849000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AB52" s="3">
         <v>920700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AC52" s="3">
         <v>838900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AD52" s="3">
         <v>868600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AE52" s="3">
         <v>911400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AF52" s="3">
         <v>914100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AG52" s="3">
         <v>942300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AH52" s="3">
         <v>930900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AI52" s="3">
         <v>928600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AJ52" s="3">
         <v>858600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AK52" s="3">
         <v>843700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AL52" s="3">
         <v>926800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AM52" s="3">
         <v>2890200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AN52" s="3">
         <v>913300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AO52" s="3">
         <v>961400</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AP52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ52" s="3">
         <v>921400</v>
       </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5428,121 +5919,145 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>10</v>
+      <c r="D54" s="3">
+        <v>36172700</v>
       </c>
       <c r="E54" s="3">
+        <v>36568700</v>
+      </c>
+      <c r="F54" s="3">
+        <v>36090200</v>
+      </c>
+      <c r="G54" s="3">
+        <v>35750300</v>
+      </c>
+      <c r="H54" s="3">
+        <v>32952400</v>
+      </c>
+      <c r="I54" s="3">
         <v>31279700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>30779600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>31941800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>31473300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>31388500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>31361800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>30100600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>29222700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>28721200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>29123200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>29083800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>27654100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>25688500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>26037800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>25296400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>23643100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>22579100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>21874700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>22832800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>24953500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>16672300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>17064000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>16636600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>15234400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AG54" s="3">
         <v>13049800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AH54" s="3">
         <v>13164500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AI54" s="3">
         <v>12868800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AJ54" s="3">
         <v>11653100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AK54" s="3">
         <v>11299600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AL54" s="3">
         <v>11144700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AM54" s="3">
         <v>11158200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AN54" s="3">
         <v>10821600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AO54" s="3">
         <v>11121800</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM54" s="3">
+      <c r="AP54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ54" s="3">
         <v>10666400</v>
       </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5582,8 +6097,12 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5623,686 +6142,762 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>10</v>
+      <c r="D57" s="3">
+        <v>2430000</v>
       </c>
       <c r="E57" s="3">
+        <v>2384400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2443300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2359500</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2229000</v>
+      </c>
+      <c r="I57" s="3">
         <v>2133600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>2179300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>2219500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>2092600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>2161000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>2387500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>2926500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>2394100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>2257700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>2256200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>2442400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>2027100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>1928000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>1825000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>1701000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>1351100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>1299500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>1150400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>1204000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AB57" s="3">
         <v>1190200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AC57" s="3">
         <v>997000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AD57" s="3">
         <v>1077500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AE57" s="3">
         <v>1334000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AF57" s="3">
         <v>1269300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AG57" s="3">
         <v>1327000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AH57" s="3">
         <v>1407700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AI57" s="3">
         <v>1397000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AJ57" s="3">
         <v>1110100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AK57" s="3">
         <v>1073700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AL57" s="3">
         <v>1069300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AM57" s="3">
         <v>1144400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AN57" s="3">
         <v>987400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AO57" s="3">
         <v>971900</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AP57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ57" s="3">
         <v>1006000</v>
       </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>10</v>
+      <c r="D58" s="3">
+        <v>1004200</v>
       </c>
       <c r="E58" s="3">
+        <v>2180300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1332600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>1324700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>1321200</v>
+      </c>
+      <c r="I58" s="3">
         <v>516600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>601500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>639100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>1150800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>1775800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>1259000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>425500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>426900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>894200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="R58" s="3">
         <v>912700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>894800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="T58" s="3">
         <v>899900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="U58" s="3">
         <v>77000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="V58" s="3">
         <v>984100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="W58" s="3">
         <v>974600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="X58" s="3">
         <v>938400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="Y58" s="3">
         <v>912600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="Z58" s="3">
         <v>385900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="AA58" s="3">
         <v>585400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="AB58" s="3">
         <v>705800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AC58" s="3">
         <v>263100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AD58" s="3">
         <v>280200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AE58" s="3">
         <v>26900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AF58" s="3">
         <v>32900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AG58" s="3">
         <v>32900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AH58" s="3">
         <v>26000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AI58" s="3">
         <v>29600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AJ58" s="3">
         <v>350300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AK58" s="3">
         <v>359000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AL58" s="3">
         <v>354500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AM58" s="3">
         <v>1506800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AN58" s="3">
         <v>22400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AO58" s="3">
         <v>142000</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AP58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ58" s="3">
         <v>20000</v>
       </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>10</v>
+      <c r="D59" s="3">
+        <v>3368000</v>
       </c>
       <c r="E59" s="3">
+        <v>3063500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>2929400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2654000</v>
+      </c>
+      <c r="H59" s="3">
+        <v>2823300</v>
+      </c>
+      <c r="I59" s="3">
         <v>2558400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>2412300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>2542900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>2586500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>2214900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>2319000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>2256600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>2739100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>2516300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>2623900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>2701800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="T59" s="3">
         <v>2540700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>2086500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>1985600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>2141100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>1919200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>1708800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>1631200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>1791400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>1604700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>1253300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>967800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>1349900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AF59" s="3">
         <v>1167000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AG59" s="3">
         <v>845800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AH59" s="3">
         <v>1057500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AI59" s="3">
         <v>1154500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AJ59" s="3">
         <v>795000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AK59" s="3">
         <v>695600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AL59" s="3">
         <v>711300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AM59" s="3">
         <v>3932600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AN59" s="3">
         <v>802200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AO59" s="3">
         <v>694900</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AP59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ59" s="3">
         <v>770000</v>
       </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>10</v>
+      <c r="D60" s="3">
+        <v>6802200</v>
       </c>
       <c r="E60" s="3">
+        <v>7628300</v>
+      </c>
+      <c r="F60" s="3">
+        <v>6705400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6786300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>6373500</v>
+      </c>
+      <c r="I60" s="3">
         <v>5208600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>5193100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>5739500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>5829900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>6151700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>5965500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>6000200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>5560000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>5668200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>5792700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>6039000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>5467700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>4091500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>4794600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>4816700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="X60" s="3">
         <v>4208700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Y60" s="3">
         <v>3920900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>3167500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AA60" s="3">
         <v>3580800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AB60" s="3">
         <v>3500700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AC60" s="3">
         <v>2513400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AD60" s="3">
         <v>2325500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AE60" s="3">
         <v>2710900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AF60" s="3">
         <v>2469300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AG60" s="3">
         <v>2205800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AH60" s="3">
         <v>2491200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AI60" s="3">
         <v>2581100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AJ60" s="3">
         <v>2255300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AK60" s="3">
         <v>2128400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AL60" s="3">
         <v>2135100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AM60" s="3">
         <v>4049300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AN60" s="3">
         <v>1812000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AO60" s="3">
         <v>1808800</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM60" s="3">
+      <c r="AP60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ60" s="3">
         <v>1795900</v>
       </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>7268400</v>
       </c>
       <c r="E61" s="3">
+        <v>7382700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>7202100</v>
+      </c>
+      <c r="G61" s="3">
+        <v>7141900</v>
+      </c>
+      <c r="H61" s="3">
+        <v>4986500</v>
+      </c>
+      <c r="I61" s="3">
         <v>5849500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>4926000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>5124900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>5016600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>5038300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>5121000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>4987300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>5084100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>5421600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>5541300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>5641300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="T61" s="3">
         <v>6101000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="U61" s="3">
         <v>6681400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="V61" s="3">
         <v>6601100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="W61" s="3">
         <v>6523000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="X61" s="3">
         <v>6587100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="Y61" s="3">
         <v>6411600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Z61" s="3">
         <v>6757700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="AA61" s="3">
         <v>7019300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AB61" s="3">
         <v>8053100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AC61" s="3">
         <v>1743300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AD61" s="3">
         <v>1800100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AE61" s="3">
         <v>1879100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AF61" s="3">
         <v>1772800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AG61" s="3">
         <v>1789300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AH61" s="3">
         <v>1787400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AI61" s="3">
         <v>1782600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AJ61" s="3">
         <v>1658000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AK61" s="3">
         <v>1648200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AL61" s="3">
         <v>1675100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AM61" s="3">
         <v>2259700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AN61" s="3">
         <v>2063300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AO61" s="3">
         <v>2225500</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="3">
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="3">
         <v>2056500</v>
       </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>10</v>
+      <c r="D62" s="3">
+        <v>1011100</v>
       </c>
       <c r="E62" s="3">
+        <v>1015800</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1202300</v>
+      </c>
+      <c r="G62" s="3">
+        <v>1261300</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1305900</v>
+      </c>
+      <c r="I62" s="3">
         <v>1132700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>1150200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>1167700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>990000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>948300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>575900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>490100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>545900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>515000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>1248300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>1253600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>1290500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>1447400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>1576500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>1596900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>1573200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>1510800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>1566900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>1626400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AB62" s="3">
         <v>1989800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AC62" s="3">
         <v>1181000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AD62" s="3">
         <v>1323800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AE62" s="3">
         <v>1471200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AF62" s="3">
         <v>1277600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AG62" s="3">
         <v>1215200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AH62" s="3">
         <v>893100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AI62" s="3">
         <v>880100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AJ62" s="3">
         <v>803700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AK62" s="3">
         <v>814600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AL62" s="3">
         <v>788800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AM62" s="3">
         <v>880800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AN62" s="3">
         <v>777500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AO62" s="3">
         <v>820500</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AP62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ62" s="3">
         <v>917900</v>
       </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6414,8 +7009,20 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6527,8 +7134,20 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6640,121 +7259,145 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>10</v>
+      <c r="D66" s="3">
+        <v>15585500</v>
       </c>
       <c r="E66" s="3">
+        <v>16497200</v>
+      </c>
+      <c r="F66" s="3">
+        <v>15610000</v>
+      </c>
+      <c r="G66" s="3">
+        <v>15744500</v>
+      </c>
+      <c r="H66" s="3">
+        <v>13324700</v>
+      </c>
+      <c r="I66" s="3">
         <v>12786400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>11900800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>12737000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>12480400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>12829900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>12312400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>12060800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>11747800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>12217500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>12582300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>12933800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>12859200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>12220400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>12972300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>12936600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>12369100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>11843300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>11492200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>12226500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>13543600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>5437700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>5449500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>6061300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>5519700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AG66" s="3">
         <v>5210300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AH66" s="3">
         <v>5171600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AI66" s="3">
         <v>5243800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AJ66" s="3">
         <v>4717000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AK66" s="3">
         <v>4591200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AL66" s="3">
         <v>4599000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AM66" s="3">
         <v>4834700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AN66" s="3">
         <v>4652900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AO66" s="3">
         <v>4854900</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM66" s="3">
+      <c r="AP66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ66" s="3">
         <v>4770400</v>
       </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6794,8 +7437,12 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6907,8 +7554,20 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7020,8 +7679,20 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7133,8 +7804,20 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7246,121 +7929,145 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>10</v>
+      <c r="D72" s="3">
+        <v>9304200</v>
       </c>
       <c r="E72" s="3">
+        <v>8905800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>9236800</v>
+      </c>
+      <c r="G72" s="3">
+        <v>8888900</v>
+      </c>
+      <c r="H72" s="3">
+        <v>8600100</v>
+      </c>
+      <c r="I72" s="3">
         <v>7599400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>7484200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>7782700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>7629900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>7223000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>7438900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>6566500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>5947600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>5022800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>5018500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>3788900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>3543900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>2225300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>2013800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>1525300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>421100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>673700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-90900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>451500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>424400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>875100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>784500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>515700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>365900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AG72" s="3">
         <v>144700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AH72" s="3">
         <v>36700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AI72" s="3">
         <v>-327700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AJ72" s="3">
         <v>-461200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AK72" s="3">
         <v>-844900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AL72" s="3">
         <v>-1325100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AM72" s="3">
         <v>-3115800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AN72" s="3">
         <v>-1713300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AO72" s="3">
         <v>-2158600</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AP72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ72" s="3">
         <v>-2713800</v>
       </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7472,8 +8179,20 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7585,8 +8304,20 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7698,121 +8429,145 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>10</v>
+      <c r="D76" s="3">
+        <v>20587200</v>
       </c>
       <c r="E76" s="3">
+        <v>20071500</v>
+      </c>
+      <c r="F76" s="3">
+        <v>20480200</v>
+      </c>
+      <c r="G76" s="3">
+        <v>20005900</v>
+      </c>
+      <c r="H76" s="3">
+        <v>19627700</v>
+      </c>
+      <c r="I76" s="3">
         <v>18493300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>18878800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>19204800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>18992800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>18558600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>19049400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>18039800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>17474900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>16503700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>16540900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>16150000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>14794900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>13468100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>13065600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>12359800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>11274000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>10735800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>10382600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>10606300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>11409800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>11234500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>11614600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>10575300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>9714700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AG76" s="3">
         <v>7839500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AH76" s="3">
         <v>7992900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AI76" s="3">
         <v>7625000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AJ76" s="3">
         <v>6936100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AK76" s="3">
         <v>6708400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AL76" s="3">
         <v>6545700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AM76" s="3">
         <v>6323500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AN76" s="3">
         <v>6168700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AO76" s="3">
         <v>6267000</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM76" s="3">
+      <c r="AP76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ76" s="3">
         <v>5896000</v>
       </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7924,126 +8679,150 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8077,86 +8856,98 @@
       <c r="M81" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R81" s="3">
         <v>798600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>786700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>554900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>501300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>488300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>499800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>250700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>199100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>253200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>105900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>-150500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>189700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>235800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>197200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>263500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>271700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>300500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>168000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AJ81" s="3">
         <v>297600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AK81" s="3">
         <v>512700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AL81" s="3">
         <v>230000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AM81" s="3">
         <v>679900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AN81" s="3">
         <v>283900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AO81" s="3">
         <v>423700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AP81" s="3">
         <v>190200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AQ81" s="3">
         <v>264100</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8196,121 +8987,137 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>543700</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" s="3">
+        <v>504200</v>
+      </c>
+      <c r="G83" s="3">
+        <v>404900</v>
+      </c>
+      <c r="H83" s="3">
         <v>503600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="I83" s="3">
         <v>502800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="J83" s="3">
         <v>504000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="K83" s="3">
         <v>378900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>481400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>471500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>458500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>342200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>441100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>449900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>475200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>479800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="T83" s="3">
         <v>459200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="U83" s="3">
         <v>439400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="V83" s="3">
         <v>426400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="W83" s="3">
         <v>430400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="X83" s="3">
         <v>402000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>375700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Z83" s="3">
         <v>375700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="AA83" s="3">
         <v>393400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="AB83" s="3">
         <v>416700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AC83" s="3">
         <v>281100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AD83" s="3">
         <v>291900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AE83" s="3">
         <v>298900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AF83" s="3">
         <v>280000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AG83" s="3">
         <v>274100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AH83" s="3">
         <v>272100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AI83" s="3">
         <v>267300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AJ83" s="3">
         <v>240500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AK83" s="3">
         <v>237900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AL83" s="3">
         <v>228900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AM83" s="3">
         <v>230000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AN83" s="3">
         <v>226600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AO83" s="3">
         <v>475400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AP83" s="3">
         <v>234800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AQ83" s="3">
         <v>238300</v>
       </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8422,8 +9229,20 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8535,8 +9354,20 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8648,8 +9479,20 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8761,8 +9604,20 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8874,121 +9729,145 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>10</v>
+      <c r="D89" s="3">
+        <v>1272700</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F89" s="3">
+        <v>487300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>1639100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>754000</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J89" s="3">
         <v>558000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>1219000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>1166800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>803800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>-162500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>1748500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>1127700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>701900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>697800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>1703200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>1082700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>666200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>862600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>1052700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>810400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>756400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Z89" s="3">
         <v>599200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="AA89" s="3">
         <v>774300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AB89" s="3">
         <v>580400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AC89" s="3">
         <v>397400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AD89" s="3">
         <v>211300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AE89" s="3">
         <v>837900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AF89" s="3">
         <v>464700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AG89" s="3">
         <v>250600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AH89" s="3">
         <v>365500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AI89" s="3">
         <v>760600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AJ89" s="3">
         <v>506200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AK89" s="3">
         <v>344500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AL89" s="3">
         <v>184000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AM89" s="3">
         <v>690000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AN89" s="3">
         <v>593500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AO89" s="3">
         <v>679600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AP89" s="3">
         <v>331000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AQ89" s="3">
         <v>518800</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9028,121 +9907,137 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>10</v>
+      <c r="D91" s="3">
+        <v>-482100</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F91" s="3">
+        <v>-546000</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-437600</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-427500</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J91" s="3">
         <v>-688500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-713800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-681500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-617100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-645500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-1040400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-769700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-547600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-605000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-866000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="T91" s="3">
         <v>-542000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="U91" s="3">
         <v>-494000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="V91" s="3">
         <v>-408000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="W91" s="3">
         <v>-597000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="X91" s="3">
         <v>-245500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="Y91" s="3">
         <v>-269500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Z91" s="3">
         <v>-237800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="AA91" s="3">
         <v>-285400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="AB91" s="3">
         <v>-236700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AC91" s="3">
         <v>-234900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AD91" s="3">
         <v>-251000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AE91" s="3">
         <v>-374800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AF91" s="3">
         <v>-360000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AG91" s="3">
         <v>-369400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AH91" s="3">
         <v>-436500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AI91" s="3">
         <v>-436500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AJ91" s="3">
         <v>-265700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AK91" s="3">
         <v>-250200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AL91" s="3">
         <v>-287200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AM91" s="3">
         <v>-362400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AN91" s="3">
         <v>-209800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AO91" s="3">
         <v>-495300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AP91" s="3">
         <v>-238300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AQ91" s="3">
         <v>-325100</v>
       </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9254,8 +10149,20 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9367,121 +10274,145 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>10</v>
+      <c r="D94" s="3">
+        <v>-285600</v>
       </c>
       <c r="E94" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F94" s="3">
+        <v>-565900</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-3684100</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-144500</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1120200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="K94" s="3">
         <v>-561000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-535700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-388400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-888700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-1414100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-153900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-195600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-673400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-1269800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="T94" s="3">
         <v>-660500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>-141100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="V94" s="3">
         <v>-574000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-890000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-697200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>-474700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Z94" s="3">
         <v>-346100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="AA94" s="3">
         <v>-762900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AB94" s="3">
         <v>-5681500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AC94" s="3">
         <v>-215700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AD94" s="3">
         <v>-1211800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AE94" s="3">
         <v>-463000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AF94" s="3">
         <v>-2329300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AG94" s="3">
         <v>76500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AH94" s="3">
         <v>-230700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AI94" s="3">
         <v>-449500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AJ94" s="3">
         <v>-427100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AK94" s="3">
         <v>-142500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AL94" s="3">
         <v>-299600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AM94" s="3">
         <v>-537400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AN94" s="3">
         <v>-458900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AO94" s="3">
         <v>-285200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AP94" s="3">
         <v>-314600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AQ94" s="3">
         <v>-495300</v>
       </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9521,8 +10452,12 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9541,33 +10476,33 @@
       <c r="H96" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I96" s="3">
+      <c r="I96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M96" s="3">
         <v>492000</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q96" s="3">
         <v>453100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -9626,16 +10561,28 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-291100</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM96" s="3">
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9747,8 +10694,20 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9860,8 +10819,20 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9973,343 +10944,391 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>10</v>
+      <c r="D100" s="3">
+        <v>-1254400</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F100" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>2143600</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-520300</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J100" s="3">
         <v>-24800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-580000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-677200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-224400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>823500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-22200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>-861400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-506300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-27700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-632200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="T100" s="3">
         <v>-66400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="U100" s="3">
         <v>-1302000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="V100" s="3">
         <v>-25000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="W100" s="3">
         <v>-354500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="X100" s="3">
         <v>-64500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="Y100" s="3">
         <v>-311300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>-196000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>-587500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="AB100" s="3">
         <v>6578200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AC100" s="3">
         <v>-404200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AD100" s="3">
         <v>1363500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AE100" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AF100" s="3">
         <v>1763400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AG100" s="3">
         <v>-357600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AH100" s="3">
         <v>-22500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AI100" s="3">
         <v>-353700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AJ100" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AK100" s="3">
         <v>-234500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AL100" s="3">
         <v>-14600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AM100" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AN100" s="3">
         <v>-116700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AO100" s="3">
         <v>-282900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AP100" s="3">
         <v>9400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AQ100" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="H101" s="3">
         <v>1100</v>
-      </c>
-      <c r="E101" s="3">
-        <v>2200</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-7700</v>
-      </c>
-      <c r="G101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-5500</v>
       </c>
       <c r="I101" s="3">
         <v>2200</v>
       </c>
       <c r="J101" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="K101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N101" s="3">
         <v>-15000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>26500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>-17800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="R101" s="3">
         <v>-15500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="S101" s="3">
         <v>30300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="T101" s="3">
         <v>-18500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="U101" s="3">
         <v>4300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="V101" s="3">
         <v>4300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="W101" s="3">
         <v>6500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="X101" s="3">
         <v>1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="Y101" s="3">
         <v>8200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="Z101" s="3">
         <v>-13300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="AA101" s="3">
         <v>-44600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="AB101" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AC101" s="3">
         <v>-19200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AD101" s="3">
         <v>12800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AE101" s="3">
         <v>2400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AF101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AG101" s="3">
         <v>9400</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AJ101" s="3">
         <v>-6600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AK101" s="3">
         <v>11200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AL101" s="3">
         <v>1100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AM101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AN101" s="3">
         <v>-13500</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AO101" s="3">
         <v>1200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AP101" s="3">
         <v>-15300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AQ101" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-265100</v>
       </c>
       <c r="E102" s="3">
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>-123300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>97400</v>
+      </c>
+      <c r="H102" s="3">
+        <v>75200</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-571500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>69200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-45000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>193100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-235400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>314400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>107000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-18800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-168600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>337300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>-772500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>268000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>-185400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>49700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>-21400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>43900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>-620700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AB102" s="3">
         <v>1440000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AC102" s="3">
         <v>-241600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AD102" s="3">
         <v>375900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AE102" s="3">
         <v>366300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AF102" s="3">
         <v>-102300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AG102" s="3">
         <v>-21200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AH102" s="3">
         <v>112400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AI102" s="3">
         <v>-46100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AJ102" s="3">
         <v>49400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AK102" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AL102" s="3">
         <v>-129000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AM102" s="3">
         <v>150300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AN102" s="3">
         <v>5600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AO102" s="3">
         <v>112700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AP102" s="3">
         <v>10600</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AQ102" s="3">
         <v>17600</v>
       </c>
     </row>
